--- a/rcads/data/xls/11_InstrumentComponents.xlsx
+++ b/rcads/data/xls/11_InstrumentComponents.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_11_InstrumentComponents"/>
   </sheets>
   <definedNames>
-    <definedName name="_11_InstrumentComponents">'_11_InstrumentComponents'!$A$1:$E$661</definedName>
+    <definedName name="_11_InstrumentComponents">'_11_InstrumentComponents'!$A$1:$E$710</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E661"/>
+  <dimension ref="A1:E710"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -8727,6 +8727,9 @@
           <t>Over the last 2 weeks, how often have you been bothered by any of the following problems?</t>
         </is>
       </c>
+      <c r="E458" s="0">
+        <v>3</v>
+      </c>
     </row>
     <row outlineLevel="0" r="459">
       <c r="A459" s="0">
@@ -8743,6 +8746,9 @@
           <t>ID#:</t>
         </is>
       </c>
+      <c r="E459" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="460">
       <c r="A460" s="0">
@@ -8759,6 +8765,9 @@
           <t>DATE:</t>
         </is>
       </c>
+      <c r="E460" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row outlineLevel="0" r="461">
       <c r="A461" s="0">
@@ -12532,6 +12541,937 @@
       </c>
       <c r="E661" s="0">
         <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="662">
+      <c r="A662" s="0">
+        <v>670</v>
+      </c>
+      <c r="B662" s="0">
+        <v>122</v>
+      </c>
+      <c r="C662" s="0">
+        <v>2</v>
+      </c>
+      <c r="D662" s="0" t="inlineStr">
+        <is>
+          <t>তারিখঃ</t>
+        </is>
+      </c>
+      <c r="E662" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="663">
+      <c r="A663" s="0">
+        <v>671</v>
+      </c>
+      <c r="B663" s="0">
+        <v>122</v>
+      </c>
+      <c r="C663" s="0">
+        <v>1</v>
+      </c>
+      <c r="D663" s="0" t="inlineStr">
+        <is>
+          <t>নামঃ</t>
+        </is>
+      </c>
+      <c r="E663" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="664">
+      <c r="A664" s="0">
+        <v>672</v>
+      </c>
+      <c r="B664" s="0">
+        <v>122</v>
+      </c>
+      <c r="C664" s="0">
+        <v>4</v>
+      </c>
+      <c r="D664" s="0" t="inlineStr">
+        <is>
+          <t>নির্দেশনা: নিচের পদ/বাক্যগুলো পড়ে এগুলোর আপনার ক্ষেত্রে কতটুকু ঘন ঘন ঘটে তা নির্দেশ করুন (✓ চিহ্ন দিন)। আপনার উত্তরগুলো সঠিক না ভুল তা নিয়ে চিন্তা করার প্রয়োজন নেই।</t>
+        </is>
+      </c>
+      <c r="E664" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="665">
+      <c r="A665" s="0">
+        <v>673</v>
+      </c>
+      <c r="B665" s="0">
+        <v>116</v>
+      </c>
+      <c r="C665" s="0">
+        <v>2</v>
+      </c>
+      <c r="D665" s="0" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="E665" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="666">
+      <c r="A666" s="0">
+        <v>674</v>
+      </c>
+      <c r="B666" s="0">
+        <v>116</v>
+      </c>
+      <c r="C666" s="0">
+        <v>1</v>
+      </c>
+      <c r="D666" s="0" t="inlineStr">
+        <is>
+          <t>姓名/编號</t>
+        </is>
+      </c>
+      <c r="E666" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="667">
+      <c r="A667" s="0">
+        <v>675</v>
+      </c>
+      <c r="B667" s="0">
+        <v>116</v>
+      </c>
+      <c r="C667" s="0">
+        <v>4</v>
+      </c>
+      <c r="D667" s="0" t="inlineStr">
+        <is>
+          <t>指示: 以下是一些有關兒童及青少年的描述。請根據你的情況, 圈出一個能夠反映到每件事發 生在你身上的答案。答案是沒有對與錯之分。</t>
+        </is>
+      </c>
+      <c r="E667" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="668">
+      <c r="A668" s="0">
+        <v>676</v>
+      </c>
+      <c r="B668" s="0">
+        <v>118</v>
+      </c>
+      <c r="C668" s="0">
+        <v>2</v>
+      </c>
+      <c r="D668" s="0" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="E668" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="669">
+      <c r="A669" s="0">
+        <v>677</v>
+      </c>
+      <c r="B669" s="0">
+        <v>118</v>
+      </c>
+      <c r="C669" s="0">
+        <v>1</v>
+      </c>
+      <c r="D669" s="0" t="inlineStr">
+        <is>
+          <t>姓名/编號</t>
+        </is>
+      </c>
+      <c r="E669" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="670">
+      <c r="A670" s="0">
+        <v>678</v>
+      </c>
+      <c r="B670" s="0">
+        <v>118</v>
+      </c>
+      <c r="C670" s="0">
+        <v>4</v>
+      </c>
+      <c r="D670" s="0" t="inlineStr">
+        <is>
+          <t>指示: 以下是一些有關兒童及青少年的描述。請根據你的情況, 圈出一個能夠反映到每件事發生在你身 上的答案。答案是沒有對與錯之分。</t>
+        </is>
+      </c>
+      <c r="E670" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="671">
+      <c r="A671" s="0">
+        <v>679</v>
+      </c>
+      <c r="B671" s="0">
+        <v>126</v>
+      </c>
+      <c r="C671" s="0">
+        <v>4</v>
+      </c>
+      <c r="D671" s="0" t="inlineStr">
+        <is>
+          <t>Sila bulatkan perkataan yang menunjukkan kekerapan perkara-perkara berikut berlaku kepada anda. Tiada jawapan yang betul atau salah.</t>
+        </is>
+      </c>
+      <c r="E671" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="672">
+      <c r="A672" s="0">
+        <v>680</v>
+      </c>
+      <c r="B672" s="0">
+        <v>177</v>
+      </c>
+      <c r="C672" s="0">
+        <v>3</v>
+      </c>
+      <c r="D672" s="0" t="inlineStr">
+        <is>
+          <t>Faqa</t>
+        </is>
+      </c>
+      <c r="E672" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="673">
+      <c r="A673" s="0">
+        <v>681</v>
+      </c>
+      <c r="B673" s="0">
+        <v>177</v>
+      </c>
+      <c r="C673" s="0">
+        <v>4</v>
+      </c>
+      <c r="D673" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem qarkoni fjalën që përshkruan sa shpesh ju ndodhin këto gjëra. Nuk ka përgjigje të sakta ose të gabuara.</t>
+        </is>
+      </c>
+      <c r="E673" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="674">
+      <c r="A674" s="0">
+        <v>682</v>
+      </c>
+      <c r="B674" s="0">
+        <v>177</v>
+      </c>
+      <c r="C674" s="0">
+        <v>1</v>
+      </c>
+      <c r="D674" s="0" t="inlineStr">
+        <is>
+          <t>Emri/ID:</t>
+        </is>
+      </c>
+      <c r="E674" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="675">
+      <c r="A675" s="0">
+        <v>683</v>
+      </c>
+      <c r="B675" s="0">
+        <v>177</v>
+      </c>
+      <c r="C675" s="0">
+        <v>2</v>
+      </c>
+      <c r="D675" s="0" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="E675" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="676">
+      <c r="A676" s="0">
+        <v>684</v>
+      </c>
+      <c r="B676" s="0">
+        <v>177</v>
+      </c>
+      <c r="C676" s="0">
+        <v>5</v>
+      </c>
+      <c r="D676" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem zgjidhni fjalën që përshkruan sa shpesh ju ndodhin këto gjëra. Nuk ka përgjigje të sakta ose të gabuara.</t>
+        </is>
+      </c>
+      <c r="E676" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="677">
+      <c r="A677" s="0">
+        <v>685</v>
+      </c>
+      <c r="B677" s="0">
+        <v>178</v>
+      </c>
+      <c r="C677" s="0">
+        <v>1</v>
+      </c>
+      <c r="D677" s="0" t="inlineStr">
+        <is>
+          <t>Emri/ID:</t>
+        </is>
+      </c>
+      <c r="E677" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="678">
+      <c r="A678" s="0">
+        <v>686</v>
+      </c>
+      <c r="B678" s="0">
+        <v>178</v>
+      </c>
+      <c r="C678" s="0">
+        <v>2</v>
+      </c>
+      <c r="D678" s="0" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="E678" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="679">
+      <c r="A679" s="0">
+        <v>687</v>
+      </c>
+      <c r="B679" s="0">
+        <v>178</v>
+      </c>
+      <c r="C679" s="0">
+        <v>6</v>
+      </c>
+      <c r="D679" s="0" t="inlineStr">
+        <is>
+          <t>Marrëdhënia me fëmijën:</t>
+        </is>
+      </c>
+      <c r="E679" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="680">
+      <c r="A680" s="0">
+        <v>688</v>
+      </c>
+      <c r="B680" s="0">
+        <v>178</v>
+      </c>
+      <c r="C680" s="0">
+        <v>4</v>
+      </c>
+      <c r="D680" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem qarkoni fjalën që përshkruan sa shpesh i ndodhin fëmijës suaj këto gjëra.</t>
+        </is>
+      </c>
+      <c r="E680" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="681">
+      <c r="A681" s="0">
+        <v>689</v>
+      </c>
+      <c r="B681" s="0">
+        <v>178</v>
+      </c>
+      <c r="C681" s="0">
+        <v>5</v>
+      </c>
+      <c r="D681" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem zgjidhni fjalën që përshkruan sa shpesh i ndodhin fëmijës suaj këto gjëra.</t>
+        </is>
+      </c>
+      <c r="E681" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="682">
+      <c r="A682" s="0">
+        <v>690</v>
+      </c>
+      <c r="B682" s="0">
+        <v>178</v>
+      </c>
+      <c r="C682" s="0">
+        <v>3</v>
+      </c>
+      <c r="D682" s="0" t="inlineStr">
+        <is>
+          <t>Faqa</t>
+        </is>
+      </c>
+      <c r="E682" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="683">
+      <c r="A683" s="0">
+        <v>691</v>
+      </c>
+      <c r="B683" s="0">
+        <v>179</v>
+      </c>
+      <c r="C683" s="0">
+        <v>1</v>
+      </c>
+      <c r="D683" s="0" t="inlineStr">
+        <is>
+          <t>Emri/ID:</t>
+        </is>
+      </c>
+      <c r="E683" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="684">
+      <c r="A684" s="0">
+        <v>692</v>
+      </c>
+      <c r="B684" s="0">
+        <v>179</v>
+      </c>
+      <c r="C684" s="0">
+        <v>2</v>
+      </c>
+      <c r="D684" s="0" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="E684" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="685">
+      <c r="A685" s="0">
+        <v>693</v>
+      </c>
+      <c r="B685" s="0">
+        <v>179</v>
+      </c>
+      <c r="C685" s="0">
+        <v>4</v>
+      </c>
+      <c r="D685" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem qarkoni fjalën që përshkruan sa shpesh ju ndodhin këto gjëra. Nuk ka përgjigje të sakta ose të gabuara.</t>
+        </is>
+      </c>
+      <c r="E685" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="686">
+      <c r="A686" s="0">
+        <v>694</v>
+      </c>
+      <c r="B686" s="0">
+        <v>179</v>
+      </c>
+      <c r="C686" s="0">
+        <v>5</v>
+      </c>
+      <c r="D686" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem zgjidhni fjalën që përshkruan sa shpesh ju ndodhin këto gjëra. Nuk ka përgjigje të sakta ose të gabuara.</t>
+        </is>
+      </c>
+      <c r="E686" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="687">
+      <c r="A687" s="0">
+        <v>695</v>
+      </c>
+      <c r="B687" s="0">
+        <v>179</v>
+      </c>
+      <c r="C687" s="0">
+        <v>3</v>
+      </c>
+      <c r="D687" s="0" t="inlineStr">
+        <is>
+          <t>Faqa</t>
+        </is>
+      </c>
+      <c r="E687" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="688">
+      <c r="A688" s="0">
+        <v>696</v>
+      </c>
+      <c r="B688" s="0">
+        <v>180</v>
+      </c>
+      <c r="C688" s="0">
+        <v>3</v>
+      </c>
+      <c r="D688" s="0" t="inlineStr">
+        <is>
+          <t>Faqa</t>
+        </is>
+      </c>
+      <c r="E688" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="689">
+      <c r="A689" s="0">
+        <v>697</v>
+      </c>
+      <c r="B689" s="0">
+        <v>180</v>
+      </c>
+      <c r="C689" s="0">
+        <v>1</v>
+      </c>
+      <c r="D689" s="0" t="inlineStr">
+        <is>
+          <t>Emri/ID:</t>
+        </is>
+      </c>
+      <c r="E689" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="690">
+      <c r="A690" s="0">
+        <v>698</v>
+      </c>
+      <c r="B690" s="0">
+        <v>180</v>
+      </c>
+      <c r="C690" s="0">
+        <v>2</v>
+      </c>
+      <c r="D690" s="0" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="E690" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="691">
+      <c r="A691" s="0">
+        <v>699</v>
+      </c>
+      <c r="B691" s="0">
+        <v>180</v>
+      </c>
+      <c r="C691" s="0">
+        <v>6</v>
+      </c>
+      <c r="D691" s="0" t="inlineStr">
+        <is>
+          <t>Marrëdhënia me fëmijën:</t>
+        </is>
+      </c>
+      <c r="E691" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="692">
+      <c r="A692" s="0">
+        <v>700</v>
+      </c>
+      <c r="B692" s="0">
+        <v>180</v>
+      </c>
+      <c r="C692" s="0">
+        <v>4</v>
+      </c>
+      <c r="D692" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem qarkoni fjalën që përshkruan sa shpesh i ndodhin fëmijës suaj këto gjëra.</t>
+        </is>
+      </c>
+      <c r="E692" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="693">
+      <c r="A693" s="0">
+        <v>701</v>
+      </c>
+      <c r="B693" s="0">
+        <v>180</v>
+      </c>
+      <c r="C693" s="0">
+        <v>5</v>
+      </c>
+      <c r="D693" s="0" t="inlineStr">
+        <is>
+          <t>Ju lutem zgjidhni fjalën që përshkruan sa shpesh i ndodhin fëmijës suaj këto gjëra.</t>
+        </is>
+      </c>
+      <c r="E693" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="694">
+      <c r="A694" s="0">
+        <v>703</v>
+      </c>
+      <c r="B694" s="0">
+        <v>181</v>
+      </c>
+      <c r="C694" s="0">
+        <v>4</v>
+      </c>
+      <c r="D694" s="0" t="inlineStr">
+        <is>
+          <t>Over the last 2 weeks, how often have you been bothered by any of the following problems?</t>
+        </is>
+      </c>
+      <c r="E694" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="695">
+      <c r="A695" s="0">
+        <v>704</v>
+      </c>
+      <c r="B695" s="0">
+        <v>182</v>
+      </c>
+      <c r="C695" s="0">
+        <v>4</v>
+      </c>
+      <c r="D695" s="0" t="inlineStr">
+        <is>
+          <t>Over the last 2 weeks , how often have you been bothered by any of the following problems?</t>
+        </is>
+      </c>
+      <c r="E695" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="696">
+      <c r="A696" s="0">
+        <v>705</v>
+      </c>
+      <c r="B696" s="0">
+        <v>182</v>
+      </c>
+      <c r="C696" s="0">
+        <v>7</v>
+      </c>
+      <c r="D696" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E696" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="697">
+      <c r="A697" s="0">
+        <v>706</v>
+      </c>
+      <c r="B697" s="0">
+        <v>183</v>
+      </c>
+      <c r="C697" s="0">
+        <v>4</v>
+      </c>
+      <c r="D697" s="0" t="inlineStr">
+        <is>
+          <t>Over the last 2 weeks, how often have you been bothered by any of the following problems?</t>
+        </is>
+      </c>
+      <c r="E697" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="698">
+      <c r="A698" s="0">
+        <v>707</v>
+      </c>
+      <c r="B698" s="0">
+        <v>184</v>
+      </c>
+      <c r="C698" s="0">
+        <v>4</v>
+      </c>
+      <c r="D698" s="0" t="inlineStr">
+        <is>
+          <t>Over the previous 2 weeks, how often have you been bothered by any of the following problems?</t>
+        </is>
+      </c>
+      <c r="E698" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="699">
+      <c r="A699" s="0">
+        <v>708</v>
+      </c>
+      <c r="B699" s="0">
+        <v>182</v>
+      </c>
+      <c r="C699" s="0">
+        <v>7</v>
+      </c>
+      <c r="D699" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E699" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="700">
+      <c r="A700" s="0">
+        <v>709</v>
+      </c>
+      <c r="B700" s="0">
+        <v>184</v>
+      </c>
+      <c r="C700" s="0">
+        <v>7</v>
+      </c>
+      <c r="D700" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E700" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="701">
+      <c r="A701" s="0">
+        <v>710</v>
+      </c>
+      <c r="B701" s="0">
+        <v>183</v>
+      </c>
+      <c r="C701" s="0">
+        <v>7</v>
+      </c>
+      <c r="D701" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E701" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="702">
+      <c r="A702" s="0">
+        <v>711</v>
+      </c>
+      <c r="B702" s="0">
+        <v>106</v>
+      </c>
+      <c r="C702" s="0">
+        <v>7</v>
+      </c>
+      <c r="D702" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E702" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="703">
+      <c r="A703" s="0">
+        <v>712</v>
+      </c>
+      <c r="B703" s="0">
+        <v>185</v>
+      </c>
+      <c r="C703" s="0">
+        <v>4</v>
+      </c>
+      <c r="D703" s="0" t="inlineStr">
+        <is>
+          <t>Over the previous 2 weeks, how often have you been bothered by any of the following problems?</t>
+        </is>
+      </c>
+      <c r="E703" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="704">
+      <c r="A704" s="0">
+        <v>713</v>
+      </c>
+      <c r="B704" s="0">
+        <v>185</v>
+      </c>
+      <c r="C704" s="0">
+        <v>7</v>
+      </c>
+      <c r="D704" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E704" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="705">
+      <c r="A705" s="0">
+        <v>714</v>
+      </c>
+      <c r="B705" s="0">
+        <v>186</v>
+      </c>
+      <c r="C705" s="0">
+        <v>4</v>
+      </c>
+      <c r="D705" s="0" t="inlineStr">
+        <is>
+          <t>Over the last 2 weeks, how often have you been bothered by any of the following problems?</t>
+        </is>
+      </c>
+      <c r="E705" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="706">
+      <c r="A706" s="0">
+        <v>715</v>
+      </c>
+      <c r="B706" s="0">
+        <v>186</v>
+      </c>
+      <c r="C706" s="0">
+        <v>7</v>
+      </c>
+      <c r="D706" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E706" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="707">
+      <c r="A707" s="0">
+        <v>716</v>
+      </c>
+      <c r="B707" s="0">
+        <v>187</v>
+      </c>
+      <c r="C707" s="0">
+        <v>4</v>
+      </c>
+      <c r="D707" s="0" t="inlineStr">
+        <is>
+          <t>Over the last 2 weeks, how often have you been bothered by any of the following problems?</t>
+        </is>
+      </c>
+      <c r="E707" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="708">
+      <c r="A708" s="0">
+        <v>717</v>
+      </c>
+      <c r="B708" s="0">
+        <v>187</v>
+      </c>
+      <c r="C708" s="0">
+        <v>7</v>
+      </c>
+      <c r="D708" s="0" t="inlineStr">
+        <is>
+          <t>(Use “✔” to indicate your answer)</t>
+        </is>
+      </c>
+      <c r="E708" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="709">
+      <c r="A709" s="0">
+        <v>718</v>
+      </c>
+      <c r="B709" s="0">
+        <v>188</v>
+      </c>
+      <c r="C709" s="0">
+        <v>4</v>
+      </c>
+      <c r="D709" s="0" t="inlineStr">
+        <is>
+          <t>Au cours des 2 dernières semaines, selon quelle fréquence avez-vous été gêné(e) par les problèmes suivants ?</t>
+        </is>
+      </c>
+      <c r="E709" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="710">
+      <c r="A710" s="0">
+        <v>719</v>
+      </c>
+      <c r="B710" s="0">
+        <v>188</v>
+      </c>
+      <c r="C710" s="0">
+        <v>7</v>
+      </c>
+      <c r="D710" s="0" t="inlineStr">
+        <is>
+          <t>(Veuillez cocher (✔) votre réponse)</t>
+        </is>
+      </c>
+      <c r="E710" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
